--- a/diseases/d239/2015-2019.xlsx
+++ b/diseases/d239/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.03853734586747662</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.03853734586747662</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.03853734586747662</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.05780601880121494</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01926867293373831</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.03853734586747662</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.03853734586747662</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.05780601880121494</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -6152,9 +6113,6 @@
       <c r="O29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.07639444207515571</v>
       </c>
@@ -6787,9 +6745,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -7422,9 +7377,6 @@
       <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.05729583155636678</v>
       </c>
@@ -8057,9 +8009,6 @@
       <c r="O38" t="n">
         <v>5</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.09549305259394464</v>
       </c>
@@ -8692,9 +8641,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -9327,9 +9273,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9962,9 +9905,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -10597,9 +10537,6 @@
       <c r="O50" t="n">
         <v>5</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.09549305259394464</v>
       </c>
@@ -11232,9 +11169,6 @@
       <c r="O53" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.05729583155636678</v>
       </c>
@@ -11867,9 +11801,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.03819722103757785</v>
       </c>
@@ -12502,9 +12433,6 @@
       <c r="O59" t="n">
         <v>4</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.07639444207515571</v>
       </c>
@@ -13137,9 +13065,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.05685261102722718</v>
       </c>
@@ -13772,9 +13697,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -14407,9 +14329,6 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -15042,9 +14961,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -15677,9 +15593,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -16312,9 +16225,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -16947,9 +16857,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -17582,9 +17489,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -18217,9 +18121,6 @@
       <c r="O86" t="n">
         <v>2</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.03790174068481812</v>
       </c>
@@ -18852,9 +18753,6 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.01895087034240906</v>
       </c>
@@ -19487,9 +19385,6 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.03790174068481812</v>
       </c>
@@ -20122,9 +20017,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -20757,9 +20649,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -21392,9 +21281,6 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -22027,9 +21913,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -22662,9 +22545,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -23297,9 +23177,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -23932,9 +23809,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -24567,9 +24441,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -25202,9 +25073,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -25837,9 +25705,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -26472,9 +26337,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.018826178365803</v>
       </c>
@@ -27107,9 +26969,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -27742,9 +27601,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -28377,9 +28233,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -29012,9 +28865,6 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -29647,9 +29497,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -30282,9 +30129,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -30917,9 +30761,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -31552,9 +31393,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -32187,9 +32025,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -32822,9 +32657,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -33457,9 +33289,6 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -34092,9 +33921,6 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -34727,9 +34553,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -35360,9 +35183,6 @@
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
